--- a/04_RHEL_구성표/RHEL_구성표_변경목록.xlsx
+++ b/04_RHEL_구성표/RHEL_구성표_변경목록.xlsx
@@ -18,17 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공통'!$A$3:$C$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공통'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RHEL7 구성 확인'!$A$3:$J$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'RHEL7 구성 확인'!$A$3:$J$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'RHEL7 구성 확인'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RHEL8 구성 확인'!$A$3:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RHEL8 구성 확인'!$A$3:$J$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'RHEL8 구성 확인'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RHEL9 구성 확인'!$A$3:$J$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RHEL9 구성 확인'!$A$3:$J$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'RHEL9 구성 확인'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'대표 정보'!$A$3:$F$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'대표 정보'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'패키지'!$A$3:$H$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'패키지'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'고민·요청 이력'!$A$3:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'고민·요청 이력'!$A$3:$F$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'고민·요청 이력'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1869,14 +1869,26 @@
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 DNS 미사용</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>비고: (없음)</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="n"/>
     </row>
     <row r="34">
@@ -2677,35 +2689,27 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>SSH 설정</t>
+          <t>sudo 권한</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+          <t>egrep -v '^#|^$' /etc/sudoers /etc/sudoers.d/*</t>
         </is>
       </c>
       <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>allowusers 없으면 미설정</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
-        </is>
-      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="3" t="n"/>
     </row>
     <row r="56">
@@ -2719,23 +2723,35 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>접근제어 (hosts.allow)</t>
+          <t>SSH 설정</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>cat /etc/hosts.allow</t>
+          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
         </is>
       </c>
       <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>allowusers 없으면 미설정</t>
+        </is>
+      </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="4" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+        </is>
+      </c>
       <c r="J56" s="3" t="n"/>
     </row>
     <row r="57">
@@ -2749,12 +2765,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>접근제어 (hosts.deny)</t>
+          <t>접근제어 (hosts.allow)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>cat /etc/hosts.deny</t>
+          <t>cat /etc/hosts.allow</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2779,12 +2795,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>방화벽 실행</t>
+          <t>접근제어 (hosts.deny)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-active firewalld</t>
+          <t>cat /etc/hosts.deny</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2794,11 +2810,7 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
+      <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr"/>
       <c r="J58" s="3" t="n"/>
     </row>
@@ -2813,12 +2825,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>방화벽 부팅 시 시작</t>
+          <t>방화벽 실행</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-enabled firewalld</t>
+          <t>systemctl is-active firewalld</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2847,20 +2859,16 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>방화벽 응답</t>
+          <t>방화벽 부팅 시 시작</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>firewall-cmd --state</t>
+          <t>systemctl is-enabled firewalld</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>not running이면 미사용</t>
-        </is>
-      </c>
+      <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -2885,31 +2893,31 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>방화벽 영역</t>
+          <t>방화벽 응답</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>firewall-cmd --get-active-zones</t>
+          <t>firewall-cmd --state</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>not running이면 미사용</t>
+        </is>
+      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo firewall-cmd --get-active-zones</t>
-        </is>
-      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="3" t="n"/>
     </row>
     <row r="62">
@@ -2923,20 +2931,16 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>방화벽 규칙</t>
+          <t>방화벽 영역</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
+          <t>firewall-cmd --get-active-zones</t>
         </is>
       </c>
       <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>활성 영역마다</t>
-        </is>
-      </c>
+      <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -2944,13 +2948,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>명령, 결과 칸</t>
+          <t>명령</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo firewall-cmd --zone=&lt;zone&gt; --list-all
-결과: 명령 출력 시트</t>
+          <t>명령: sudo firewall-cmd --get-active-zones</t>
         </is>
       </c>
       <c r="J62" s="3" t="n"/>
@@ -2966,18 +2969,18 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>방화벽 저장 규칙</t>
+          <t>방화벽 규칙</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
+          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>규칙과 다르면 표시</t>
+          <t>활성 영역마다</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -2992,7 +2995,7 @@
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo firewall-cmd --permanent --zone=&lt;zone&gt; --list-all
+          <t>명령: sudo firewall-cmd --zone=&lt;zone&gt; --list-all
 결과: 명령 출력 시트</t>
         </is>
       </c>
@@ -3009,23 +3012,36 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>보안 모듈 (SELinux)</t>
+          <t>방화벽 저장 규칙</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>getenforce</t>
+          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
         </is>
       </c>
       <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>규칙과 다르면 표시</t>
+        </is>
+      </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="4" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo firewall-cmd --permanent --zone=&lt;zone&gt; --list-all
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
       <c r="J64" s="3" t="n"/>
     </row>
     <row r="65">
@@ -3039,12 +3055,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>보안 모듈 부팅 설정</t>
+          <t>보안 모듈 (SELinux)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>grep ^SELINUX= /etc/selinux/config</t>
+          <t>getenforce</t>
         </is>
       </c>
       <c r="E65" s="3" t="n"/>
@@ -3064,17 +3080,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>업데이트·패키지</t>
+          <t>계정·접근</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>주요 패키지</t>
+          <t>보안 모듈 부팅 설정</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
+          <t>grep ^SELINUX= /etc/selinux/config</t>
         </is>
       </c>
       <c r="E66" s="3" t="n"/>
@@ -3084,11 +3100,7 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
+      <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="3" t="n"/>
     </row>
@@ -3103,19 +3115,15 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>전체 패키지</t>
+          <t>주요 패키지</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>패키지 시트 참고</t>
-        </is>
-      </c>
+          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -3141,35 +3149,31 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>최근 패치일</t>
+          <t>전체 패키지</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>yum history</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Action(s)에 U가 든 줄</t>
-        </is>
-      </c>
+          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>패키지 시트 참고</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo yum history | head -6</t>
-        </is>
-      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
       <c r="J68" s="3" t="n"/>
     </row>
     <row r="69">
@@ -3183,18 +3187,18 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>자동 업데이트 설정</t>
+          <t>최근 패치일</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>egrep 'download_updates|apply_updates' /etc/yum/yum-cron.conf /etc/yum/yum-cron-hourly.conf</t>
+          <t>yum history</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>파일 없으면 미설치</t>
+          <t>Action(s)에 U가 든 줄</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -3202,8 +3206,16 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="4" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo yum history | head -6</t>
+        </is>
+      </c>
       <c r="J69" s="3" t="n"/>
     </row>
     <row r="70">
@@ -3217,26 +3229,26 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>자동 업데이트 실행</t>
+          <t>자동 업데이트 설정</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-active yum-cron</t>
+          <t>egrep 'download_updates|apply_updates' /etc/yum/yum-cron.conf /etc/yum/yum-cron-hourly.conf</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 미설치</t>
+        </is>
+      </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
+      <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="3" t="n"/>
     </row>
@@ -3251,12 +3263,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>자동 업데이트 부팅 시 시작</t>
+          <t>자동 업데이트 실행</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-enabled yum-cron</t>
+          <t>systemctl is-active yum-cron</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3285,12 +3297,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>저장소 목록</t>
+          <t>자동 업데이트 부팅 시 시작</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>yum repolist</t>
+          <t>systemctl is-enabled yum-cron</t>
         </is>
       </c>
       <c r="E72" s="3" t="n"/>
@@ -3300,7 +3312,11 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr"/>
       <c r="J72" s="3" t="n"/>
     </row>
@@ -3315,12 +3331,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>저장소 파일</t>
+          <t>저장소 목록</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>ls /etc/yum.repos.d/</t>
+          <t>yum repolist</t>
         </is>
       </c>
       <c r="E73" s="3" t="n"/>
@@ -3345,30 +3361,22 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>구독 등록 여부</t>
+          <t>저장소 파일</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>ls /etc/pki/consumer/cert.pem</t>
+          <t>ls /etc/yum.repos.d/</t>
         </is>
       </c>
       <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>파일 없으면 미등록</t>
-        </is>
-      </c>
+      <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
+      <c r="H74" s="3" t="inlineStr"/>
       <c r="I74" s="4" t="inlineStr"/>
       <c r="J74" s="3" t="n"/>
     </row>
@@ -3383,18 +3391,18 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>구독 (RHSM)</t>
+          <t>구독 등록 여부</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>subscription-manager status</t>
+          <t>ls /etc/pki/consumer/cert.pem</t>
         </is>
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>RHEL</t>
+          <t>파일 없으면 미등록</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -3402,16 +3410,12 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo subscription-manager status</t>
-        </is>
-      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="3" t="n"/>
     </row>
     <row r="76">
@@ -3425,18 +3429,18 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>릴리스 고정</t>
+          <t>구독 (RHSM)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>subscription-manager release --show</t>
+          <t>subscription-manager status</t>
         </is>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Release not set이면 미고정</t>
+          <t>RHEL</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -3451,7 +3455,7 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo subscription-manager release --show</t>
+          <t>명령: sudo subscription-manager status</t>
         </is>
       </c>
       <c r="J76" s="3" t="n"/>
@@ -3462,80 +3466,84 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>커널 설정</t>
+          <t>업데이트·패키지</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>sysctl</t>
+          <t>릴리스 고정</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+          <t>subscription-manager release --show</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
+          <t>Release not set이면 미고정</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo subscription-manager release --show</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>sysctl</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
           <t>99-sysctl.conf 줄은 중복</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>명령, 비고, 결과 칸</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>명령: cat /etc/sysctl.conf /etc/sysctl.d/*.conf | grep -v '^#' | grep .
 비고: (없음)
 결과: 명령 출력 시트</t>
         </is>
       </c>
-      <c r="J77" s="3" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>자원 제한 (limits)</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>명령: cat /etc/security/limits.conf /etc/security/limits.d/* | grep -v '^#' | grep .</t>
-        </is>
-      </c>
       <c r="J78" s="3" t="n"/>
     </row>
     <row r="79">
@@ -3549,12 +3557,12 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>kdump 설정</t>
+          <t>자원 제한 (limits)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
+          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3564,12 +3572,16 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /etc/security/limits.conf /etc/security/limits.d/* | grep -v '^#' | grep .</t>
+        </is>
+      </c>
       <c r="J79" s="3" t="n"/>
     </row>
     <row r="80">
@@ -3583,12 +3595,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>kdump 실행</t>
+          <t>kdump 설정</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-active kdump</t>
+          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3617,12 +3629,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>kdump 부팅 시 시작</t>
+          <t>kdump 실행</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>systemctl is-enabled kdump</t>
+          <t>systemctl is-active kdump</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3646,17 +3658,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>서비스·예약</t>
+          <t>커널 설정</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>실행 중인 서비스</t>
+          <t>kdump 부팅 시 시작</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>systemctl list-units --type=service --state=running --no-pager</t>
+          <t>systemctl is-enabled kdump</t>
         </is>
       </c>
       <c r="E82" s="3" t="n"/>
@@ -3666,17 +3678,12 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>비고, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>비고: 업무 서비스는 서비스 시트
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
       <c r="J82" s="3" t="n"/>
     </row>
     <row r="83">
@@ -3690,12 +3697,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>자동 시작 서비스</t>
+          <t>실행 중인 서비스</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
+          <t>systemctl list-units --type=service --state=running --no-pager</t>
         </is>
       </c>
       <c r="E83" s="3" t="n"/>
@@ -3707,12 +3714,13 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>결과 칸</t>
+          <t>비고, 결과 칸</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>결과: 명령 출력 시트</t>
+          <t>비고: 업무 서비스는 서비스 시트
+결과: 명령 출력 시트</t>
         </is>
       </c>
       <c r="J83" s="3" t="n"/>
@@ -3728,12 +3736,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>열린 포트</t>
+          <t>자동 시작 서비스</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>ss -tulnp</t>
+          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
         </is>
       </c>
       <c r="E84" s="3" t="n"/>
@@ -3743,12 +3751,16 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
       <c r="J84" s="3" t="n"/>
     </row>
     <row r="85">
@@ -3762,12 +3774,12 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>예약 작업 (타이머)</t>
+          <t>열린 포트</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>systemctl list-timers --all --no-pager</t>
+          <t>ss -tulnp</t>
         </is>
       </c>
       <c r="E85" s="3" t="n"/>
@@ -3777,16 +3789,12 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="3" t="n"/>
     </row>
     <row r="86">
@@ -3800,67 +3808,75 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
+          <t>예약 작업 (타이머)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>systemctl list-timers --all --no-pager</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
           <t>예약 작업 (crontab)</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>tail -v -n +1 /var/spool/cron/*</t>
         </is>
       </c>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>파일명이 계정명</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>항목명, 명령, 비고</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>항목: 예약 작업 (cron)
 명령: sudo crontab -l
 비고: root</t>
         </is>
       </c>
-      <c r="J86" s="3" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>예약 작업 (cron.d)</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>ls /etc/cron.d</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
       <c r="J87" s="3" t="n"/>
     </row>
     <row r="88">
@@ -3869,25 +3885,21 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>에이전트·백업</t>
+          <t>서비스·예약</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>모니터링 에이전트</t>
+          <t>예약 작업 (cron.d)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>pgrep -fa &lt;에이전트 이름&gt;</t>
+          <t>ls /etc/cron.d</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
+      <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -3908,7 +3920,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>보안 에이전트</t>
+          <t>모니터링 에이전트</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -3942,7 +3954,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>백신</t>
+          <t>보안 에이전트</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3976,18 +3988,18 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>설정 백업</t>
+          <t>백신</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>백업 위치, 마지막 백업 날짜</t>
+          <t>pgrep -fa &lt;에이전트 이름&gt;</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>직접 입력</t>
+          <t>출력 없으면 미실행</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -4005,23 +4017,23 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>특수 구성</t>
+          <t>에이전트·백업</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>GPU</t>
+          <t>설정 백업</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>nvidia-smi -L</t>
+          <t>백업 위치, 마지막 백업 날짜</t>
         </is>
       </c>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>GPU 서버</t>
+          <t>직접 입력</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -4029,69 +4041,75 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>구분 이동</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>구분: CPU·메모리</t>
-        </is>
-      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
       <c r="J92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n"/>
+      <c r="A93" s="3" t="n">
+        <v>90</v>
+      </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>특수 구성</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>IPv6 경로</t>
+          <t>GPU</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>ip -6 route</t>
+          <t>nvidia-smi -L</t>
         </is>
       </c>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>IPv6 사용 시</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="6" t="inlineStr">
-        <is>
-          <t>삭제</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="n"/>
+          <t>GPU 서버</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>구분 이동</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>구분: CPU·메모리</t>
+        </is>
+      </c>
       <c r="J93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>계정·접근</t>
+          <t>네트워크</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>방화벽 서비스</t>
+          <t>IPv6 경로</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>systemctl status firewalld | egrep 'Loaded|Active'</t>
+          <t>ip -6 route</t>
         </is>
       </c>
       <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>IPv6 사용 시</t>
+        </is>
+      </c>
       <c r="G94" s="3" t="n"/>
       <c r="H94" s="6" t="inlineStr">
         <is>
@@ -4105,17 +4123,17 @@
       <c r="A95" s="3" t="n"/>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>업데이트·패키지</t>
+          <t>계정·접근</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>자동 업데이트 예약</t>
+          <t>방화벽 서비스</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>systemctl status yum-cron | egrep 'Loaded|Active'</t>
+          <t>systemctl status firewalld | egrep 'Loaded|Active'</t>
         </is>
       </c>
       <c r="E95" s="3" t="n"/>
@@ -4138,20 +4156,16 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>버전 고정 패키지</t>
+          <t>자동 업데이트 예약</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>yum versionlock list</t>
+          <t>systemctl status yum-cron | egrep 'Loaded|Active'</t>
         </is>
       </c>
       <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>플러그인 없으면 미사용</t>
-        </is>
-      </c>
+      <c r="F96" s="3" t="n"/>
       <c r="G96" s="3" t="n"/>
       <c r="H96" s="6" t="inlineStr">
         <is>
@@ -4161,14 +4175,3330 @@
       <c r="I96" s="4" t="n"/>
       <c r="J96" s="3" t="n"/>
     </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>버전 고정 패키지</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>yum versionlock list</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n"/>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>플러그인 없으면 미사용</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J96"/>
+  <autoFilter ref="A3:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RHEL 8 구성 확인 (최종 순서, 삭제 행은 맨 아래)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>결과 칸 고정 값</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>결과 칸 서식</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>변경 전</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>호스트명</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>hostname</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>OS 버전</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>cat /etc/redhat-release</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>OS 설치일</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>rpm -qi filesystem | grep -i 'install date'</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>VM 템플릿 배포는 템플릿 생성일</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>실행 커널</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>uname -r</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>설치된 커널</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>rpm -q kernel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>실행 커널보다 최신이면 재부팅 필요</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>아키텍처</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>uname -m</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>부팅 방식</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ls /sys/firmware/efi</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>경로가 있으면 UEFI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>부팅 옵션</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>cat /proc/cmdline</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>마지막 부팅</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>uptime -s</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>장비 모델</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>cat /sys/class/dmi/id/product_name</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>시리얼번호</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>cat /sys/class/dmi/id/product_serial</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo cat /sys/class/dmi/id/product_serial</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>기본</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>가상화</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>systemd-detect-virt</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>none이면 물리</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>CPU 모델</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>grep -i 'model name' /proc/cpuinfo | uniq</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>명령: lscpu | grep -i '^model name'</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>CPU 소켓 수</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>grep -i 'physical id' /proc/cpuinfo | sort -u | wc -l</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>숫자만</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>명령: lscpu | grep 'Socket(s):'</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>소켓당 코어 수</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>grep -i 'cpu cores' /proc/cpuinfo | uniq</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>숫자만</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>명령: lscpu | grep -i 'core(s) per socket'</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>물리 코어 수</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>CPU 소켓 수 × 소켓당 코어 수</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>수식</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>수식</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>논리 CPU 수</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>grep -i '^processor' /proc/cpuinfo | wc -l</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>숫자만</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>명령: lscpu | grep -i '^cpu(s):'</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>하이퍼스레딩</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>논리 CPU 수 = 물리 코어 수 × 2</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>수식</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>수식</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>OS 인식 메모리 (MiB)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>free -m</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Mem total, 숫자만</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>CPU·메모리</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>물리 메모리</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>dmidecode -t memory | grep '^.Size: [0-9]' | cut -d' ' -f2-</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>물리 서버</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo dmidecode -t memory | grep -i size | egrep -v 'No Module|Cache|Logical|Volatile'</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>시간대</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>timedatectl | grep 'Time zone'</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>시간 동기화 여부</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>timedatectl | egrep 'synchronized|NTP'</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>타임 서버 (chrony)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>chronyc sources -v</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>* 표시가 동기 서버</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>IP 주소</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ip -br addr</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>MAC 주소</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ip -br link</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>MTU</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ip link | grep mtu</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>본딩 상태</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>tail -v -n +1 /proc/net/bonding/*</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>본딩 사용 시</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /proc/net/bonding/&lt;본드 이름&gt;
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>IPv4 경로</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ip route</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr"/>
+      <c r="J31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>DNS 서버·도메인</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>cat /etc/resolv.conf</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 DNS 미사용</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>비고: (없음)</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>호스트 파일</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>cat /etc/hosts</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>네트워크 연결</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>nmcli connection show</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>저장된 네트워크 설정</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>tail -v -n +1 /etc/sysconfig/network-scripts/ifcfg-*</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>keyfile이면 /etc/NetworkManager/system-connections</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /etc/sysconfig/network-scripts/ifcfg-*
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>저장된 정적 경로</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>tail -v -n +1 /etc/sysconfig/network-scripts/route-*</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 없음</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /etc/sysconfig/network-scripts/route-*</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>링 버퍼 (RX/TX)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ethtool -g &lt;인터페이스&gt;</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>조정한 경우</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo ethtool -g &lt;인터페이스&gt;</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>장치와 파일시스템</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>파일시스템 사용량</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>현재 마운트</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>저장된 마운트</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>cat /etc/fstab</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>스왑</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>cat /proc/swaps</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>LVM-PV</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>pvs</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LVM 사용 시</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo pvs</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>LVM-VG</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>vgs</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo vgs</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>LVM-LV</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>lvs -a -o +devices</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo lvs -a -o +devices</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>SCSI 호스트</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>lsscsi -H</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>lsscsi 패키지</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>디스크</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>SCSI 장치</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>lsscsi -is</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>lsscsi 패키지</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>HBA 포트 (WWPN·상태·유형)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>SAN 사용 시</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>항목명, 명령</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>항목: HBA WWPN
+명령: cat /sys/class/fc_host/host*/port_name</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>멀티패스 상태</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>multipath -ll</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo multipath -ll
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>멀티패스 설정</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo cat /etc/multipath.conf
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>멀티패스 이름 매핑</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>cat /etc/multipath/bindings</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo cat /etc/multipath/bindings
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>로그인 가능 계정</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>관리자 그룹</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>getent group wheel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>sudo 권한</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/sudoers /etc/sudoers.d/*</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>SSH 설정</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>allowusers 없으면 미설정</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 실행</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>systemctl is-active firewalld</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 부팅 시 시작</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>systemctl is-enabled firewalld</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 응답</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>firewall-cmd --state</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>not running이면 미사용</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 영역</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>firewall-cmd --get-active-zones</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo firewall-cmd --get-active-zones</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 규칙</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>활성 영역마다</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo firewall-cmd --zone=&lt;zone&gt; --list-all
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 저장 규칙</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>규칙과 다르면 표시</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>명령, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo firewall-cmd --permanent --zone=&lt;zone&gt; --list-all
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>보안 모듈 (SELinux)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>getenforce</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>보안 모듈 부팅 설정</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>grep ^SELINUX= /etc/selinux/config</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>주요 패키지</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>전체 패키지</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>패키지 시트 참고</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>최근 패치일</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>dnf history</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Action(s)에 U가 든 줄</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo dnf history | head -5</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>자동 업데이트 설정</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 미설치</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>자동 업데이트 예약</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>systemctl list-unit-files 'dnf-automatic*'</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>enabled면 사용</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>저장소 목록</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>dnf repolist</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>저장소 파일</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>ls /etc/yum.repos.d/</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>구독 등록 여부</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>ls /etc/pki/consumer/cert.pem</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 미등록</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>구독 (RHSM)</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>subscription-manager status</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>RHEL</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo subscription-manager status</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>릴리스 고정</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>subscription-manager release --show</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Release not set이면 미고정</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo subscription-manager release --show</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>sysctl</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>99-sysctl.conf 줄은 중복</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>명령, 비고, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /etc/sysctl.conf /etc/sysctl.d/*.conf | grep -v '^#' | grep .
+비고: (없음)
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>자원 제한 (limits)</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>명령: cat /etc/security/limits.conf /etc/security/limits.d/* | grep -v '^#' | grep .</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>kdump 설정</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>kdump 실행</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>systemctl is-active kdump</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr"/>
+      <c r="J77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>커널 설정</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>kdump 부팅 시 시작</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>systemctl is-enabled kdump</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>실행 중인 서비스</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>systemctl list-units --type=service --state=running --no-pager</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>비고, 결과 칸</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>비고: 업무 서비스는 서비스 시트
+결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>자동 시작 서비스</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>열린 포트</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>ss -tulnp</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>예약 작업 (타이머)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>systemctl list-timers --all --no-pager</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>결과 칸</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>결과: 명령 출력 시트</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>예약 작업 (crontab)</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>tail -v -n +1 /var/spool/cron/*</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>파일명이 계정명</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>항목명, 명령, 비고</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>항목: 예약 작업 (cron)
+명령: sudo crontab -l
+비고: root</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>서비스·예약</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>예약 작업 (cron.d)</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>ls /etc/cron.d</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="3" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>모니터링 에이전트</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr"/>
+      <c r="J85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>보안 에이전트</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>백신</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>출력 없으면 미실행</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>에이전트·백업</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>설정 백업</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>백업 위치, 마지막 백업 날짜</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>직접 입력</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>특수 구성</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>nvidia-smi -L</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>GPU 서버</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>구분 이동</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>구분: CPU·메모리</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>IPv6 경로</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>ip -6 route</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>IPv6 사용 시</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>계정·접근</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>방화벽 서비스</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>systemctl status firewalld | egrep 'Loaded|Active'</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="n"/>
+      <c r="J91" s="3" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>업데이트·패키지</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>버전 고정 패키지</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>dnf versionlock list</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>플러그인 없으면 미사용</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="n"/>
+      <c r="J92" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J92"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4192,7 +7522,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RHEL 8 구성 확인 (최종 순서, 삭제 행은 맨 아래)</t>
+          <t>RHEL 9 구성 확인 (최종 순서, 삭제 행은 맨 아래)</t>
         </is>
       </c>
     </row>
@@ -4324,7 +7654,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>rpm -qi filesystem | grep -i 'install date'</t>
+          <t>stat -c %w /</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
@@ -5229,14 +8559,26 @@
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>파일 없으면 DNS 미사용</t>
+        </is>
+      </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>비고: (없음)</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="n"/>
     </row>
     <row r="33">
@@ -5323,13 +8665,13 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /etc/sysconfig/network-scripts/ifcfg-*</t>
+          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
         </is>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>keyfile이면 /etc/NetworkManager/system-connections</t>
+          <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5344,7 +8686,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>명령: cat /etc/sysconfig/network-scripts/ifcfg-*
+          <t>명령: sudo cat /etc/NetworkManager/system-connections/*.nmconnection
 결과: 명령 출력 시트</t>
         </is>
       </c>
@@ -5361,18 +8703,18 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>저장된 정적 경로</t>
+          <t>링 버퍼 (RX/TX)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>tail -v -n +1 /etc/sysconfig/network-scripts/route-*</t>
+          <t>ethtool -g &lt;인터페이스&gt;</t>
         </is>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>파일 없으면 없음</t>
+          <t>조정한 경우</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -5387,7 +8729,7 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>명령: cat /etc/sysconfig/network-scripts/route-*</t>
+          <t>명령: sudo ethtool -g &lt;인터페이스&gt;</t>
         </is>
       </c>
       <c r="J36" s="3" t="n"/>
@@ -5398,25 +8740,21 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>네트워크</t>
+          <t>디스크</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>링 버퍼 (RX/TX)</t>
+          <t>장치와 파일시스템</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ethtool -g &lt;인터페이스&gt;</t>
+          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>조정한 경우</t>
-        </is>
-      </c>
+      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -5424,12 +8762,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>명령</t>
+          <t>결과 칸</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo ethtool -g &lt;인터페이스&gt;</t>
+          <t>결과: 명령 출력 시트</t>
         </is>
       </c>
       <c r="J37" s="3" t="n"/>
@@ -5445,12 +8783,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>장치와 파일시스템</t>
+          <t>파일시스템 사용량</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
+          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -5483,12 +8821,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>파일시스템 사용량</t>
+          <t>현재 마운트</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
+          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
         </is>
       </c>
       <c r="E39" s="3" t="n"/>
@@ -5521,12 +8859,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>현재 마운트</t>
+          <t>저장된 마운트</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
+          <t>cat /etc/fstab</t>
         </is>
       </c>
       <c r="E40" s="3" t="n"/>
@@ -5559,12 +8897,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>저장된 마운트</t>
+          <t>스왑</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>cat /etc/fstab</t>
+          <t>cat /proc/swaps</t>
         </is>
       </c>
       <c r="E41" s="3" t="n"/>
@@ -5574,16 +8912,8 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="3" t="n"/>
     </row>
     <row r="42">
@@ -5597,23 +8927,35 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>스왑</t>
+          <t>LVM-PV</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>cat /proc/swaps</t>
+          <t>pvs</t>
         </is>
       </c>
       <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LVM 사용 시</t>
+        </is>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>명령</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>명령: sudo pvs</t>
+        </is>
+      </c>
       <c r="J42" s="3" t="n"/>
     </row>
     <row r="43">
@@ -5627,20 +8969,16 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>LVM-PV</t>
+          <t>LVM-VG</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>pvs</t>
+          <t>vgs</t>
         </is>
       </c>
       <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>LVM 사용 시</t>
-        </is>
-      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -5653,7 +8991,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo pvs</t>
+          <t>명령: sudo vgs</t>
         </is>
       </c>
       <c r="J43" s="3" t="n"/>
@@ -5669,12 +9007,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>LVM-VG</t>
+          <t>LVM-LV</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>vgs</t>
+          <t>lvs -a -o +devices</t>
         </is>
       </c>
       <c r="E44" s="3" t="n"/>
@@ -5691,7 +9029,7 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo vgs</t>
+          <t>명령: sudo lvs -a -o +devices</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
@@ -5707,31 +9045,31 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>LVM-LV</t>
+          <t>SCSI 호스트</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>lvs -a -o +devices</t>
+          <t>lsscsi -H</t>
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>lsscsi 패키지</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo lvs -a -o +devices</t>
-        </is>
-      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="3" t="n"/>
     </row>
     <row r="46">
@@ -5745,12 +9083,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>SCSI 호스트</t>
+          <t>SCSI 장치</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>lsscsi -H</t>
+          <t>lsscsi -is</t>
         </is>
       </c>
       <c r="E46" s="3" t="n"/>
@@ -5764,11 +9102,7 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
+      <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="3" t="n"/>
     </row>
@@ -5778,23 +9112,23 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>디스크</t>
+          <t>SAN</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>SCSI 장치</t>
+          <t>HBA 포트 (WWPN·상태·유형)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>lsscsi -is</t>
+          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
         </is>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>lsscsi 패키지</t>
+          <t>SAN 사용 시</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5802,8 +9136,17 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>항목명, 명령</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>항목: HBA WWPN
+명령: cat /sys/class/fc_host/host*/port_name</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="n"/>
     </row>
     <row r="48">
@@ -5817,20 +9160,16 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>HBA 포트 (WWPN·상태·유형)</t>
+          <t>멀티패스 상태</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
+          <t>multipath -ll</t>
         </is>
       </c>
       <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>SAN 사용 시</t>
-        </is>
-      </c>
+      <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
           <t>텍스트</t>
@@ -5838,13 +9177,13 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>항목명, 명령</t>
+          <t>명령, 결과 칸</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>항목: HBA WWPN
-명령: cat /sys/class/fc_host/host*/port_name</t>
+          <t>명령: sudo multipath -ll
+결과: 명령 출력 시트</t>
         </is>
       </c>
       <c r="J48" s="3" t="n"/>
@@ -5860,12 +9199,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>멀티패스 상태</t>
+          <t>멀티패스 설정</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>multipath -ll</t>
+          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
         </is>
       </c>
       <c r="E49" s="3" t="n"/>
@@ -5882,7 +9221,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo multipath -ll
+          <t>명령: sudo cat /etc/multipath.conf
 결과: 명령 출력 시트</t>
         </is>
       </c>
@@ -5899,12 +9238,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>멀티패스 설정</t>
+          <t>멀티패스 이름 매핑</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
+          <t>cat /etc/multipath/bindings</t>
         </is>
       </c>
       <c r="E50" s="3" t="n"/>
@@ -5921,7 +9260,7 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>명령: sudo cat /etc/multipath.conf
+          <t>명령: sudo cat /etc/multipath/bindings
 결과: 명령 출력 시트</t>
         </is>
       </c>
@@ -5933,17 +9272,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>SAN</t>
+          <t>계정·접근</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>멀티패스 이름 매핑</t>
+          <t>로그인 가능 계정</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>cat /etc/multipath/bindings</t>
+          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
         </is>
       </c>
       <c r="E51" s="3" t="n"/>
@@ -5953,17 +9292,8 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo cat /etc/multipath/bindings
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
+      <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="3" t="n"/>
     </row>
     <row r="52">
@@ -5977,12 +9307,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>로그인 가능 계정</t>
+          <t>관리자 그룹</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
+          <t>getent group wheel</t>
         </is>
       </c>
       <c r="E52" s="3" t="n"/>
@@ -6007,12 +9337,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>관리자 그룹</t>
+          <t>sudo 권한</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>getent group wheel</t>
+          <t>egrep -v '^#|^$' /etc/sudoers /etc/sudoers.d/*</t>
         </is>
       </c>
       <c r="E53" s="3" t="n"/>
@@ -6022,7 +9352,11 @@
           <t>텍스트</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
       <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="3" t="n"/>
     </row>
@@ -7401,3202 +10735,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:J91"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J90"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RHEL 9 구성 확인 (최종 순서, 삭제 행은 맨 아래)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>결과 칸 고정 값</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>결과 칸 서식</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>변경</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>변경 전</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>호스트명</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>hostname</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>OS 버전</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>cat /etc/redhat-release</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OS 설치일</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>stat -c %w /</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>VM 템플릿 배포는 템플릿 생성일</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>실행 커널</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>uname -r</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>설치된 커널</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>rpm -q kernel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>실행 커널보다 최신이면 재부팅 필요</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>아키텍처</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>uname -m</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>부팅 방식</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>ls /sys/firmware/efi</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>경로가 있으면 UEFI</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>부팅 옵션</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>cat /proc/cmdline</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>마지막 부팅</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>uptime -s</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>장비 모델</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>cat /sys/class/dmi/id/product_name</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>시리얼번호</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>cat /sys/class/dmi/id/product_serial</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo cat /sys/class/dmi/id/product_serial</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>기본</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>가상화</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>systemd-detect-virt</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>none이면 물리</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>CPU 모델</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>grep -i 'model name' /proc/cpuinfo | uniq</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>명령: lscpu | grep -i '^model name'</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>CPU 소켓 수</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>grep -i 'physical id' /proc/cpuinfo | sort -u | wc -l</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>숫자만</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>명령: lscpu | grep 'Socket(s):'</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>소켓당 코어 수</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>grep -i 'cpu cores' /proc/cpuinfo | uniq</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>숫자만</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>명령: lscpu | grep -i 'core(s) per socket'</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>물리 코어 수</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>CPU 소켓 수 × 소켓당 코어 수</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>수식</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>수식</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>논리 CPU 수</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>grep -i '^processor' /proc/cpuinfo | wc -l</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>숫자만</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>명령: lscpu | grep -i '^cpu(s):'</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>하이퍼스레딩</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>논리 CPU 수 = 물리 코어 수 × 2</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>수식</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>수식</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>OS 인식 메모리 (MiB)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>free -m</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Mem total, 숫자만</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>CPU·메모리</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>물리 메모리</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>dmidecode -t memory | grep '^.Size: [0-9]' | cut -d' ' -f2-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>물리 서버</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo dmidecode -t memory | grep -i size | egrep -v 'No Module|Cache|Logical|Volatile'</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>시간대</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>timedatectl | grep 'Time zone'</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>시간 동기화 여부</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>timedatectl | egrep 'synchronized|NTP'</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>타임 서버 (chrony)</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>chronyc sources -v</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>* 표시가 동기 서버</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>IP 주소</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>ip -br addr</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>MAC 주소</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>ip -br link</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr"/>
-      <c r="J28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>MTU</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>ip link | grep mtu</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>본딩 상태</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>tail -v -n +1 /proc/net/bonding/*</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>본딩 사용 시</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>명령: cat /proc/net/bonding/&lt;본드 이름&gt;
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>IPv4 경로</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>ip route</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>DNS 서버·도메인</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>cat /etc/resolv.conf</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="3" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>호스트 파일</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>cat /etc/hosts</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>네트워크 연결</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>nmcli connection show</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>저장된 네트워크 설정</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>tail -v -n +1 /etc/NetworkManager/system-connections/*.nmconnection</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>ifcfg 형식이면 /etc/sysconfig/network-scripts</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo cat /etc/NetworkManager/system-connections/*.nmconnection
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>링 버퍼 (RX/TX)</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>ethtool -g &lt;인터페이스&gt;</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>조정한 경우</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo ethtool -g &lt;인터페이스&gt;</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>장치와 파일시스템</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>lsblk -o NAME,TYPE,SIZE,FSTYPE,UUID,MOUNTPOINT,WWN</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>파일시스템 사용량</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>df -hTl -x tmpfs -x devtmpfs -x overlay -x squashfs</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>현재 마운트</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>findmnt -t ext4,xfs,nfs,nfs4,cifs -o TARGET,SOURCE,FSTYPE,OPTIONS</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>저장된 마운트</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>cat /etc/fstab</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>스왑</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>cat /proc/swaps</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>LVM-PV</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>pvs</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>LVM 사용 시</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo pvs</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>LVM-VG</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>vgs</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo vgs</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>LVM-LV</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>lvs -a -o +devices</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo lvs -a -o +devices</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>SCSI 호스트</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>lsscsi -H</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>lsscsi 패키지</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>디스크</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>SCSI 장치</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>lsscsi -is</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>lsscsi 패키지</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>HBA 포트 (WWPN·상태·유형)</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>grep . /sys/class/fc_host/host*/port_{name,state,type}</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>SAN 사용 시</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>항목명, 명령</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>항목: HBA WWPN
-명령: cat /sys/class/fc_host/host*/port_name</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>멀티패스 상태</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>multipath -ll</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo multipath -ll
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>멀티패스 설정</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>egrep -v '^#|^$' /etc/multipath.conf</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo cat /etc/multipath.conf
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>SAN</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>멀티패스 이름 매핑</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>cat /etc/multipath/bindings</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo cat /etc/multipath/bindings
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>로그인 가능 계정</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>getent passwd | egrep -v 'nologin|/bin/false|/bin/sync'</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>관리자 그룹</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>getent group wheel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>SSH 설정</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>allowusers 없으면 미설정</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo sshd -T | egrep -i '^(port|permitrootlogin|passwordauthentication|allowusers)'</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 실행</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>systemctl is-active firewalld</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 부팅 시 시작</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>systemctl is-enabled firewalld</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="3" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 응답</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>firewall-cmd --state</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>not running이면 미사용</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="3" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 영역</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>firewall-cmd --get-active-zones</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo firewall-cmd --get-active-zones</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 규칙</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>firewall-cmd --zone=&lt;zone&gt; --list-all</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>활성 영역마다</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo firewall-cmd --zone=&lt;zone&gt; --list-all
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 저장 규칙</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>firewall-cmd --permanent --zone=&lt;zone&gt; --list-all</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>규칙과 다르면 표시</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>명령, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo firewall-cmd --permanent --zone=&lt;zone&gt; --list-all
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>보안 모듈 (SELinux)</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>getenforce</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="3" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>보안 모듈 부팅 설정</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>grep ^SELINUX= /etc/selinux/config</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="3" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>주요 패키지</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>rpm -q glibc openssl openssh-server bash sudo systemd</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>전체 패키지</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>rpm -qa --qf '%{NAME} %{VERSION} %{RELEASE} %{ARCH} %{INSTALLTIME}\n' | sort</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>패키지 시트 참고</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="3" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>최근 패치일</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>dnf history</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Action(s)에 U가 든 줄</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo dnf history | head -5</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>자동 업데이트 설정</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>egrep 'download_updates|apply_updates' /etc/dnf/automatic.conf</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>파일 없으면 미설치</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="3" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>자동 업데이트 예약</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>systemctl list-unit-files 'dnf-automatic*'</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>enabled면 사용</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>저장소 목록</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>dnf repolist</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="3" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>저장소 파일</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>ls /etc/yum.repos.d/</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="3" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>구독 등록 여부</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>ls /etc/pki/consumer/cert.pem</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>파일 없으면 미등록</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="3" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>구독 (RHSM)</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>subscription-manager status</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>RHEL</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo subscription-manager status</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>릴리스 고정</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>subscription-manager release --show</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>Release not set이면 미고정</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>명령: sudo subscription-manager release --show</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>sysctl</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>egrep -v '^#|^$' /etc/sysctl.conf /etc/sysctl.d/*.conf</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>99-sysctl.conf 줄은 중복</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>명령, 비고, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>명령: cat /etc/sysctl.conf /etc/sysctl.d/*.conf | grep -v '^#' | grep .
-비고: (없음)
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>자원 제한 (limits)</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>egrep -v '^#|^$' /etc/security/limits.conf /etc/security/limits.d/*.conf</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>명령</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>명령: cat /etc/security/limits.conf /etc/security/limits.d/* | grep -v '^#' | grep .</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>kdump 설정</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>egrep -v '^#|^$' /etc/kdump.conf</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="3" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>kdump 실행</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>systemctl is-active kdump</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="3" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>커널 설정</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>kdump 부팅 시 시작</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>systemctl is-enabled kdump</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="3" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>실행 중인 서비스</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>systemctl list-units --type=service --state=running --no-pager</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>비고, 결과 칸</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>비고: 업무 서비스는 서비스 시트
-결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>자동 시작 서비스</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>systemctl list-unit-files --type=service --state=enabled --no-pager</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>열린 포트</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>ss -tulnp</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>추가</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="3" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>예약 작업 (타이머)</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>systemctl list-timers --all --no-pager</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>결과 칸</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>결과: 명령 출력 시트</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>예약 작업 (crontab)</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>tail -v -n +1 /var/spool/cron/*</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>파일명이 계정명</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>항목명, 명령, 비고</t>
-        </is>
-      </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>항목: 예약 작업 (cron)
-명령: sudo crontab -l
-비고: root</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>서비스·예약</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>예약 작업 (cron.d)</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>ls /etc/cron.d</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="3" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>에이전트·백업</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>모니터링 에이전트</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="3" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>에이전트·백업</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>보안 에이전트</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="3" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>에이전트·백업</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>백신</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>pgrep -fai &lt;에이전트 이름&gt;</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>출력 없으면 미실행</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="3" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>에이전트·백업</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>설정 백업</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>백업 위치, 마지막 백업 날짜</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>직접 입력</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="3" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>특수 구성</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>nvidia-smi -L</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>GPU 서버</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>구분 이동</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>구분: CPU·메모리</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>네트워크</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>IPv6 경로</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>ip -6 route</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>IPv6 사용 시</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>삭제</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="n"/>
-      <c r="J88" s="3" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n"/>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>계정·접근</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>방화벽 서비스</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>systemctl status firewalld | egrep 'Loaded|Active'</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>삭제</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="3" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n"/>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>업데이트·패키지</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>버전 고정 패키지</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>dnf versionlock list</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>플러그인 없으면 미사용</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="n"/>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>삭제</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:J90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -11498,7 +11636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12136,7 +12274,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>서버의 grep alias 문제. 점검 전 unalias grep egrep 실행 (현재 창에만 적용, 운영 영향 없음). 시트 명령은 그대로</t>
+          <t>서버의 grep alias 문제. 점검 전 unalias grep egrep 실행 (현재 창에만 적용, 운영 영향 없음, 2&gt;/dev/null 불필요). 시트 명령은 그대로</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -12188,12 +12326,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>RHEL은 systemd-resolved 기본 미사용. nmcli dev show | grep -i dns 로 확인 제안</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>미정</t>
+          <t>인터페이스에 DNS 미설정 서버는 파일이 없을 수 있음 (hosts 파일만 사용, 정상). DNS 행 비고에 「파일 없으면 DNS 미사용」</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>반영</t>
         </is>
       </c>
       <c r="F28" s="3" t="n"/>
@@ -12451,9 +12589,9 @@
           <t>구성 확인에 이미 있어 추가 시트는 만들지 않음</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>반영 안 함</t>
         </is>
       </c>
       <c r="F38" s="3" t="n"/>
@@ -12474,12 +12612,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>RHEL7은 pcs config --full 가능, 8·9는 --full 미지원. 직접 시험 후 결정</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>보류</t>
+          <t>양식에는 넣지 않음. 필요한 서버만 「특수 구성」에 추가 (RHEL7은 pcs config --full 가능, 8·9는 --full 미지원)</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>반영 안 함</t>
         </is>
       </c>
       <c r="F39" s="3" t="n"/>
@@ -12521,17 +12659,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>구성표 평가 후 추천 항목 (sudo 권한, 다음 부팅 커널, DNS nmcli, iptables)</t>
+          <t>sudo 권한 확인 (getent group wheel 로 충분한지)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>선택 안 함</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>미정</t>
+          <t>wheel 멤버만으로는 sudoers.d 계정별 규칙이 안 보임. sudo 권한 행 추가: egrep -v '^#|^$' /etc/sudoers /etc/sudoers.d/*</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>반영</t>
         </is>
       </c>
       <c r="F41" s="3" t="n"/>
@@ -12542,22 +12680,22 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>운영 부담</t>
+          <t>추가 검토</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>변경 때마다 전체 갱신, PM 때 파일 80개 수정</t>
+          <t>다음 부팅 커널(grubby --default-kernel)이 필요한지</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>변경 유형별로 해당 구분만 갱신. PM은 실행 커널·설치된 커널·마지막 부팅·최근 패치일·패키지 시트만</t>
+          <t>설치된 커널 중 최신이 다음 부팅 커널. 옛 커널 고정 때만 의미 있어 넣지 않음</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>반영 안 함</t>
         </is>
       </c>
       <c r="F42" s="3" t="n"/>
@@ -12568,28 +12706,80 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>추가 검토</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>iptables (firewalld 미사용 서버)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>넣지 않음</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>반영 안 함</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>운영 부담</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>변경 때마다 전체 갱신, PM 때 파일 80개 수정</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>변경 유형별로 해당 구분만 갱신. PM은 실행 커널·설치된 커널·마지막 부팅·최근 패치일·패키지 시트만</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>운영 부담</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>파일 3개(7·8·9) 유지 부담</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>버전별 차이 행은 10개 안팎. 하나로 합치는 방안은 보류</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>버전별로 각각 유지</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F43"/>
+  <autoFilter ref="A3:F45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
